--- a/master_data.xlsx
+++ b/master_data.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ricoh Scan\S.Watcharaporn\00.Web App\spc_project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ricoh Scan\S.Watcharaporn\00.Web App\spc_project\SPC Project\spc-streamlit-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="19">
   <si>
     <t>Model</t>
   </si>
@@ -41,24 +41,6 @@
     <t>USL</t>
   </si>
   <si>
-    <t>MD-101</t>
-  </si>
-  <si>
-    <t>PART-A01</t>
-  </si>
-  <si>
-    <t>MD-205</t>
-  </si>
-  <si>
-    <t>PART-B99</t>
-  </si>
-  <si>
-    <t>NEW-99</t>
-  </si>
-  <si>
-    <t>SAMPLE</t>
-  </si>
-  <si>
     <t>Unit</t>
   </si>
   <si>
@@ -71,58 +53,41 @@
     <t>Process</t>
   </si>
   <si>
-    <t>●Length</t>
-  </si>
-  <si>
-    <t>*Width</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>°</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Diameter</t>
-    </r>
-  </si>
-  <si>
-    <t>DR Thickness</t>
-  </si>
-  <si>
-    <t>●Weight</t>
-  </si>
-  <si>
     <t>mm.</t>
   </si>
   <si>
-    <t>Micrometer</t>
-  </si>
-  <si>
-    <t>4hr/1pcs</t>
-  </si>
-  <si>
     <t>Stamping</t>
   </si>
   <si>
     <t>Die no.</t>
+  </si>
+  <si>
+    <t>1934-9004</t>
+  </si>
+  <si>
+    <t>Stator Stack</t>
+  </si>
+  <si>
+    <t>☆Hole A</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mandrel + Micrometer</t>
+  </si>
+  <si>
+    <t>3 pcs/4hr.</t>
+  </si>
+  <si>
+    <t>☆I/D</t>
+  </si>
+  <si>
+    <t>☆O/D</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -141,12 +106,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -490,22 +449,22 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>3</v>
@@ -516,163 +475,111 @@
     </row>
     <row r="2" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C2" s="2">
         <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>21</v>
-      </c>
       <c r="G2" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I2" s="2">
-        <v>9.5</v>
-      </c>
-      <c r="J2" s="2">
-        <v>10.5</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
     </row>
     <row r="3" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C3" s="2">
         <v>1</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>22</v>
-      </c>
       <c r="H3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I3" s="2">
-        <v>4.8</v>
-      </c>
-      <c r="J3" s="2">
-        <v>5.2</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
     </row>
     <row r="4" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C4" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I4" s="2">
-        <v>14.95</v>
-      </c>
-      <c r="J4" s="2">
-        <v>15.05</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
     </row>
     <row r="5" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="2">
-        <v>2</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I5" s="2">
-        <v>1.9</v>
-      </c>
-      <c r="J5" s="2">
-        <v>2.1</v>
-      </c>
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
     </row>
     <row r="6" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="2">
-        <v>3</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I6" s="2">
-        <v>99</v>
-      </c>
-      <c r="J6" s="2">
-        <v>100</v>
-      </c>
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/master_data.xlsx
+++ b/master_data.xlsx
@@ -438,7 +438,9 @@
     <col min="1" max="1" width="22.44140625" customWidth="1"/>
     <col min="2" max="2" width="27.33203125" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="10" width="27.33203125" customWidth="1"/>
+    <col min="4" max="7" width="27.33203125" customWidth="1"/>
+    <col min="8" max="8" width="21.109375" customWidth="1"/>
+    <col min="9" max="10" width="27.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -498,8 +500,14 @@
       <c r="H2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
+      <c r="I2" s="2">
+        <f>5.1-0.05</f>
+        <v>5.05</v>
+      </c>
+      <c r="J2" s="2">
+        <f>5.1+0.05</f>
+        <v>5.1499999999999995</v>
+      </c>
     </row>
     <row r="3" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
@@ -526,8 +534,14 @@
       <c r="H3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
+      <c r="I3" s="2">
+        <f>38-0</f>
+        <v>38</v>
+      </c>
+      <c r="J3" s="2">
+        <f>38+0.05</f>
+        <v>38.049999999999997</v>
+      </c>
     </row>
     <row r="4" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
@@ -554,8 +568,14 @@
       <c r="H4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
+      <c r="I4" s="2">
+        <f>86-0.04</f>
+        <v>85.96</v>
+      </c>
+      <c r="J4" s="2">
+        <f>86+0</f>
+        <v>86</v>
+      </c>
     </row>
     <row r="5" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2"/>
